--- a/customboard/droneboardh7/bom.xlsx
+++ b/customboard/droneboardh7/bom.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="96">
   <si>
     <t xml:space="preserve">xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -134,24 +134,51 @@
     <t xml:space="preserve">Your Instructions / Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">C13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don’t care</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP CER 10uF 25V X7R 1206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don’t care about model/manufacturer, just make sure it fits description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP CER 100nF 16V X7R 0603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17, C18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP CER 22uF 10V X5R 0805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0805</t>
+  </si>
+  <si>
     <t xml:space="preserve">C1, C3, C5, C6, C7, C8, C9, C16</t>
   </si>
   <si>
-    <t xml:space="preserve">Don’t care</t>
-  </si>
-  <si>
     <t xml:space="preserve">CAP CER 100nF 16V X5R 0201</t>
   </si>
   <si>
     <t xml:space="preserve">0201</t>
   </si>
   <si>
-    <t xml:space="preserve">SMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don’t care about model/manufacturer, just make sure it fits description</t>
-  </si>
-  <si>
     <t xml:space="preserve">C2, C12, C15</t>
   </si>
   <si>
@@ -179,24 +206,6 @@
     <t xml:space="preserve">CAP CER 1uF 10V X5R 0201</t>
   </si>
   <si>
-    <t xml:space="preserve">C19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP CER 330nF 25V X7R 0805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP CER 100nF 16V X7R 0603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603</t>
-  </si>
-  <si>
     <t xml:space="preserve">D1</t>
   </si>
   <si>
@@ -284,6 +293,21 @@
     <t xml:space="preserve">RES 5.1K OHM 0.05W 1% 0201</t>
   </si>
   <si>
+    <t xml:space="preserve">U1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diodes Incorporated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP63205WU-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switching Voltage Regulators DCDC Conv HV Buck TSOT26 T&amp;R 3K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSOT-23-6</t>
+  </si>
+  <si>
     <t xml:space="preserve">U2</t>
   </si>
   <si>
@@ -299,21 +323,6 @@
     <t xml:space="preserve">LQFP-100 </t>
   </si>
   <si>
-    <t xml:space="preserve">U3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texas Instruments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LM7805MPX/NOPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linear Voltage Regulators 1.5-A, 30-V, linear voltage regulator 4-SOT-223 0 to 125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-223-4</t>
-  </si>
-  <si>
     <t xml:space="preserve">U4</t>
   </si>
   <si>
@@ -360,6 +369,21 @@
   </si>
   <si>
     <t xml:space="preserve">3-SMD, Non-Standard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vishay Dale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IHLP2020CZER4R7M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IND 4.7UH 4.5A 60 MOHM SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inductor SMD 2020</t>
   </si>
   <si>
     <t xml:space="preserve">Need a quick and accurante quote? Need an efficient production? Please read SMT Ordering Necessary Files &amp; Info in 1 minute. Thank you very much!</t>
@@ -376,7 +400,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,6 +467,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -467,6 +497,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u val="single"/>
@@ -545,11 +581,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -586,63 +622,83 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -730,9 +786,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>664920</xdr:colOff>
+      <xdr:colOff>664560</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>155160</xdr:rowOff>
+      <xdr:rowOff>154800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -746,7 +802,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9360" y="203760"/>
-          <a:ext cx="1375560" cy="374400"/>
+          <a:ext cx="1375200" cy="374040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1015,7 +1071,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>11</v>
@@ -1044,7 +1100,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>11</v>
@@ -1056,7 +1112,7 @@
         <v>17</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>14</v>
@@ -1070,10 +1126,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>11</v>
@@ -1082,10 +1138,10 @@
         <v>11</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>14</v>
@@ -1099,10 +1155,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>11</v>
@@ -1111,10 +1167,10 @@
         <v>11</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>14</v>
@@ -1128,10 +1184,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>11</v>
@@ -1140,10 +1196,10 @@
         <v>11</v>
       </c>
       <c r="F11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>13</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>14</v>
@@ -1157,10 +1213,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>11</v>
@@ -1169,10 +1225,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>14</v>
@@ -1186,7 +1242,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>1</v>
@@ -1198,10 +1254,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>14</v>
@@ -1215,173 +1271,171 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E14" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>34</v>
-      </c>
       <c r="G14" s="11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="9"/>
+      <c r="I14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>35</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>32</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="9"/>
+      <c r="G15" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>32</v>
+      <c r="D16" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="9"/>
+      <c r="G16" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>32</v>
+      <c r="D17" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="9"/>
+      <c r="G17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="F18" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="9"/>
+      <c r="G18" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>15</v>
-      </c>
+      <c r="G19" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="9" t="n">
+      <c r="B20" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="13" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="10" t="s">
@@ -1390,13 +1444,13 @@
       <c r="E20" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="9" t="s">
+      <c r="F20" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I20" s="12" t="s">
@@ -1407,11 +1461,11 @@
       <c r="A21" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>1</v>
+      <c r="B21" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>11</v>
@@ -1419,13 +1473,13 @@
       <c r="E21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="11" t="s">
+      <c r="F21" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="G21" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I21" s="12" t="s">
@@ -1436,10 +1490,10 @@
       <c r="A22" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="10" t="s">
@@ -1448,13 +1502,13 @@
       <c r="E22" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="9" t="s">
+      <c r="G22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="12" t="s">
@@ -1465,25 +1519,25 @@
       <c r="A23" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I23" s="12" t="s">
@@ -1494,178 +1548,448 @@
       <c r="A24" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>1</v>
+      <c r="B24" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="9"/>
+      <c r="G24" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="9" t="s">
+      <c r="F25" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="G25" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="9"/>
+      <c r="H25" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="F26" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="G26" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>75</v>
-      </c>
+      <c r="H26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="9" t="s">
+      <c r="G27" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="H27" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="F28" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" s="19" t="s">
+      <c r="D29" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="H28" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="31" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+      <c r="E29" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-    </row>
-    <row r="33" s="23" customFormat="true" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="22" t="s">
+      <c r="F29" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-    </row>
-    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="G29" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="13"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+    </row>
+    <row r="35" s="27" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="0"/>
+      <c r="D39" s="0"/>
+      <c r="E39" s="0"/>
+      <c r="F39" s="0"/>
+      <c r="G39" s="0"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="0"/>
+      <c r="D40" s="0"/>
+      <c r="E40" s="0"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="0"/>
+      <c r="D41" s="0"/>
+      <c r="E41" s="0"/>
+      <c r="F41" s="0"/>
+      <c r="G41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="0"/>
+      <c r="D42" s="0"/>
+      <c r="E42" s="0"/>
+      <c r="F42" s="0"/>
+      <c r="G42" s="0"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="0"/>
+      <c r="D43" s="0"/>
+      <c r="E43" s="0"/>
+      <c r="F43" s="0"/>
+      <c r="G43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="0"/>
+      <c r="D44" s="0"/>
+      <c r="E44" s="0"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="0"/>
+      <c r="D45" s="0"/>
+      <c r="E45" s="0"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="0"/>
+      <c r="D46" s="0"/>
+      <c r="E46" s="0"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="0"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="0"/>
+      <c r="D47" s="0"/>
+      <c r="E47" s="0"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="0"/>
+      <c r="D48" s="0"/>
+      <c r="E48" s="0"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="0"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="0"/>
+      <c r="D49" s="0"/>
+      <c r="E49" s="0"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="0"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="0"/>
+      <c r="D50" s="0"/>
+      <c r="E50" s="0"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="0"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="0"/>
+      <c r="D51" s="0"/>
+      <c r="E51" s="0"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="0"/>
+      <c r="D52" s="0"/>
+      <c r="E52" s="0"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="0"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="0"/>
+      <c r="D53" s="0"/>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0"/>
+      <c r="G53" s="0"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="0"/>
+      <c r="D54" s="0"/>
+      <c r="E54" s="0"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="0"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="0"/>
+      <c r="D55" s="0"/>
+      <c r="E55" s="0"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="0"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="0"/>
+      <c r="D56" s="0"/>
+      <c r="E56" s="0"/>
+      <c r="F56" s="0"/>
+      <c r="G56" s="0"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="0"/>
+      <c r="D57" s="0"/>
+      <c r="E57" s="0"/>
+      <c r="F57" s="0"/>
+      <c r="G57" s="0"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="0"/>
+      <c r="D58" s="0"/>
+      <c r="E58" s="0"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="0"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="0"/>
+      <c r="D59" s="0"/>
+      <c r="E59" s="0"/>
+      <c r="F59" s="0"/>
+      <c r="G59" s="0"/>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="0"/>
+      <c r="D60" s="0"/>
+      <c r="E60" s="0"/>
+      <c r="F60" s="0"/>
+      <c r="G60" s="0"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="0"/>
+      <c r="D61" s="0"/>
+      <c r="E61" s="0"/>
+      <c r="F61" s="0"/>
+      <c r="G61" s="0"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="0"/>
+      <c r="D62" s="0"/>
+      <c r="E62" s="0"/>
+      <c r="F62" s="0"/>
+      <c r="G62" s="0"/>
+    </row>
     <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1701,12 +2025,12 @@
   <mergeCells count="4">
     <mergeCell ref="A2:B3"/>
     <mergeCell ref="D2:F4"/>
-    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A35:I35"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A31" r:id="rId1" display="Need a quick and accurante quote? Need an efficient production? Please read SMT Ordering Necessary Files &amp; Info in 1 minute. Thank you very much!"/>
-    <hyperlink ref="A33" r:id="rId2" display="Click for Instructions on How to Create a BOM"/>
+    <hyperlink ref="A33" r:id="rId1" display="Need a quick and accurante quote? Need an efficient production? Please read SMT Ordering Necessary Files &amp; Info in 1 minute. Thank you very much!"/>
+    <hyperlink ref="A35" r:id="rId2" display="Click for Instructions on How to Create a BOM"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/customboard/droneboardh7/bom.xlsx
+++ b/customboard/droneboardh7/bom.xlsx
@@ -155,7 +155,7 @@
     <t xml:space="preserve">C14</t>
   </si>
   <si>
-    <t xml:space="preserve">CAP CER 100nF 16V X7R 0603</t>
+    <t xml:space="preserve">CAP CER 100nF 25V X7R 0603</t>
   </si>
   <si>
     <t xml:space="preserve">0603</t>
@@ -471,6 +471,7 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -503,6 +504,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <u val="single"/>
@@ -585,7 +587,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -622,7 +624,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -630,7 +632,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -638,14 +640,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -698,7 +692,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -786,9 +784,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>664560</xdr:colOff>
+      <xdr:colOff>663840</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:rowOff>154080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -802,7 +800,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9360" y="203760"/>
-          <a:ext cx="1375200" cy="374040"/>
+          <a:ext cx="1374480" cy="373320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1297,10 +1295,10 @@
       <c r="A15" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="10" t="s">
@@ -1309,133 +1307,133 @@
       <c r="E15" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="13"/>
+      <c r="H15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="13" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="13"/>
+      <c r="H16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="13" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="13"/>
+      <c r="H17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="13" t="s">
         <v>35</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="13"/>
+      <c r="H18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="13"/>
+      <c r="H19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="9" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="10" t="s">
@@ -1444,13 +1442,13 @@
       <c r="E20" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I20" s="12" t="s">
@@ -1461,10 +1459,10 @@
       <c r="A21" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="9" t="n">
         <v>4</v>
       </c>
       <c r="D21" s="10" t="s">
@@ -1473,13 +1471,13 @@
       <c r="E21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I21" s="12" t="s">
@@ -1490,10 +1488,10 @@
       <c r="A22" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="10" t="s">
@@ -1502,13 +1500,13 @@
       <c r="E22" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="12" t="s">
@@ -1519,10 +1517,10 @@
       <c r="A23" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="10" t="s">
@@ -1531,13 +1529,13 @@
       <c r="E23" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I23" s="12" t="s">
@@ -1548,10 +1546,10 @@
       <c r="A24" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="10" t="s">
@@ -1560,13 +1558,13 @@
       <c r="E24" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I24" s="12" t="s">
@@ -1577,10 +1575,10 @@
       <c r="A25" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="10" t="s">
@@ -1589,13 +1587,13 @@
       <c r="E25" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I25" s="12"/>
@@ -1604,37 +1602,37 @@
       <c r="A26" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="13"/>
+      <c r="H26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="10" t="s">
@@ -1646,13 +1644,13 @@
       <c r="F27" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="H27" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="13" t="s">
+      <c r="H27" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="9" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1660,335 +1658,335 @@
       <c r="A28" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H28" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="13"/>
+      <c r="H28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="H29" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="13"/>
+      <c r="H29" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F30" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="H30" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="13"/>
+      <c r="H30" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-    </row>
-    <row r="35" s="27" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="26" t="s">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+    </row>
+    <row r="35" s="25" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="0"/>
-      <c r="D39" s="0"/>
-      <c r="E39" s="0"/>
-      <c r="F39" s="0"/>
-      <c r="G39" s="0"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="0"/>
-      <c r="D40" s="0"/>
-      <c r="E40" s="0"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="0"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="0"/>
-      <c r="D41" s="0"/>
-      <c r="E41" s="0"/>
-      <c r="F41" s="0"/>
-      <c r="G41" s="0"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="0"/>
-      <c r="D42" s="0"/>
-      <c r="E42" s="0"/>
-      <c r="F42" s="0"/>
-      <c r="G42" s="0"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="0"/>
-      <c r="D43" s="0"/>
-      <c r="E43" s="0"/>
-      <c r="F43" s="0"/>
-      <c r="G43" s="0"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="0"/>
-      <c r="D44" s="0"/>
-      <c r="E44" s="0"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="0"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="0"/>
-      <c r="D45" s="0"/>
-      <c r="E45" s="0"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="0"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="26"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="0"/>
-      <c r="D46" s="0"/>
-      <c r="E46" s="0"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="0"/>
+      <c r="A46" s="26"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="26"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="0"/>
-      <c r="D47" s="0"/>
-      <c r="E47" s="0"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="0"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="26"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="0"/>
-      <c r="D48" s="0"/>
-      <c r="E48" s="0"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="0"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="26"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="0"/>
-      <c r="D49" s="0"/>
-      <c r="E49" s="0"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="0"/>
+      <c r="A49" s="26"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="0"/>
-      <c r="D50" s="0"/>
-      <c r="E50" s="0"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="0"/>
+      <c r="A50" s="26"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="0"/>
-      <c r="D51" s="0"/>
-      <c r="E51" s="0"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="0"/>
+      <c r="A51" s="26"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="0"/>
-      <c r="D52" s="0"/>
-      <c r="E52" s="0"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="0"/>
+      <c r="A52" s="26"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="0"/>
-      <c r="D53" s="0"/>
-      <c r="E53" s="0"/>
-      <c r="F53" s="0"/>
-      <c r="G53" s="0"/>
+      <c r="A53" s="26"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="0"/>
-      <c r="D54" s="0"/>
-      <c r="E54" s="0"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="0"/>
+      <c r="A54" s="26"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="26"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="0"/>
-      <c r="D55" s="0"/>
-      <c r="E55" s="0"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="0"/>
+      <c r="A55" s="26"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="26"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="0"/>
-      <c r="D56" s="0"/>
-      <c r="E56" s="0"/>
-      <c r="F56" s="0"/>
-      <c r="G56" s="0"/>
+      <c r="A56" s="26"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="0"/>
-      <c r="D57" s="0"/>
-      <c r="E57" s="0"/>
-      <c r="F57" s="0"/>
-      <c r="G57" s="0"/>
+      <c r="A57" s="26"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="0"/>
-      <c r="D58" s="0"/>
-      <c r="E58" s="0"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="0"/>
+      <c r="A58" s="26"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="26"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="0"/>
-      <c r="D59" s="0"/>
-      <c r="E59" s="0"/>
-      <c r="F59" s="0"/>
-      <c r="G59" s="0"/>
+      <c r="A59" s="26"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="0"/>
-      <c r="D60" s="0"/>
-      <c r="E60" s="0"/>
-      <c r="F60" s="0"/>
-      <c r="G60" s="0"/>
+      <c r="A60" s="26"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="0"/>
-      <c r="D61" s="0"/>
-      <c r="E61" s="0"/>
-      <c r="F61" s="0"/>
-      <c r="G61" s="0"/>
+      <c r="A61" s="26"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="0"/>
-      <c r="D62" s="0"/>
-      <c r="E62" s="0"/>
-      <c r="F62" s="0"/>
-      <c r="G62" s="0"/>
+      <c r="A62" s="26"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
     </row>
     <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
